--- a/odcs-template-v3.1.xlsx
+++ b/odcs-template-v3.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691F7C26-B267-3343-93DC-84368A54572F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FE2229-D9E8-0C4D-B44D-DD7BC1E7A83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-33240" windowWidth="60160" windowHeight="33240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="8" r:id="rId1"/>
@@ -44,9 +44,9 @@
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
-    <definedName name="quality">Quality!$A$4:$AZ$300</definedName>
+    <definedName name="quality">Quality!$A$4:$BF$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$A$4:$F$1000</definedName>
+    <definedName name="roles" localSheetId="7">Roles!$C$4:$H$1000</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
     <definedName name="schema.description" localSheetId="2">'Schema &lt;table_name&gt;'!$B$7</definedName>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="179">
   <si>
     <t>Property</t>
   </si>
@@ -434,11 +434,6 @@
   </si>
   <si>
     <t>Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This section lists team members and the history of their relation with this data contract.
-This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
-</t>
   </si>
   <si>
     <t>Access</t>
@@ -678,6 +673,22 @@
   </si>
   <si>
     <t>Arguments</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Business Impact</t>
+  </si>
+  <si>
+    <t>Server Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
+</t>
   </si>
 </sst>
 </file>
@@ -897,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1000,6 +1011,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1417,7 +1429,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1568,7 +1580,7 @@
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -1581,10 +1593,10 @@
     </row>
     <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>139</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -1597,7 +1609,7 @@
     <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="23"/>
       <c r="B19" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -1620,10 +1632,10 @@
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
@@ -1636,7 +1648,7 @@
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="25"/>
       <c r="B22" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -1649,7 +1661,7 @@
     <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -1701,7 +1713,7 @@
         <v>37</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
@@ -1781,19 +1793,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="5"/>
@@ -1803,7 +1815,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="5"/>
@@ -1846,13 +1858,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -1872,7 +1884,7 @@
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -1884,13 +1896,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1900,7 +1912,7 @@
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1912,13 +1924,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1938,7 +1950,7 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -1950,13 +1962,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -1966,7 +1978,7 @@
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="B28" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1976,7 +1988,7 @@
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -1998,13 +2010,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="7"/>
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -2026,13 +2038,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -2042,7 +2054,7 @@
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="7"/>
       <c r="B38" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -2052,7 +2064,7 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="7"/>
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -2074,13 +2086,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
       <c r="B43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -2090,7 +2102,7 @@
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
       <c r="B44" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -2110,7 +2122,7 @@
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
       <c r="B46" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -2122,13 +2134,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="7"/>
       <c r="B49" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -2138,7 +2150,7 @@
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -2148,7 +2160,7 @@
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="7"/>
       <c r="B51" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -2158,7 +2170,7 @@
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="7"/>
       <c r="B52" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
@@ -2168,7 +2180,7 @@
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="7"/>
       <c r="B53" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -2190,13 +2202,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
       <c r="B57" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -2206,7 +2218,7 @@
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
       <c r="B58" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -2216,7 +2228,7 @@
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="7"/>
       <c r="B59" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -2238,13 +2250,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="7"/>
       <c r="B63" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -2254,7 +2266,7 @@
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="7"/>
       <c r="B64" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -2264,7 +2276,7 @@
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="7"/>
       <c r="B65" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -2276,13 +2288,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="7"/>
       <c r="B68" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -2292,7 +2304,7 @@
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="7"/>
       <c r="B69" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -2302,7 +2314,7 @@
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -2312,7 +2324,7 @@
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="7"/>
       <c r="B71" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -2322,7 +2334,7 @@
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="7"/>
       <c r="B72" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -2332,7 +2344,7 @@
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="7"/>
       <c r="B73" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -2352,7 +2364,7 @@
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="7"/>
       <c r="B75" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -2362,7 +2374,7 @@
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="7"/>
       <c r="B76" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -2372,7 +2384,7 @@
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="7"/>
       <c r="B77" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -2382,7 +2394,7 @@
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="7"/>
       <c r="B78" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
@@ -2392,7 +2404,7 @@
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="7"/>
       <c r="B79" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -2402,7 +2414,7 @@
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
@@ -2412,7 +2424,7 @@
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
       <c r="B81" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -2432,7 +2444,7 @@
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -2442,7 +2454,7 @@
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
       <c r="B84" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
@@ -2452,7 +2464,7 @@
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
       <c r="B85" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
@@ -2462,7 +2474,7 @@
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="7"/>
       <c r="B86" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
@@ -2521,7 +2533,7 @@
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" s="5"/>
     </row>
@@ -2736,7 +2748,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -3086,13 +3098,13 @@
         <v>80</v>
       </c>
       <c r="AA13" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB13" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC13" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="AB13" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC13" s="10" t="s">
-        <v>144</v>
       </c>
       <c r="AD13" s="10" t="s">
         <v>83</v>
@@ -3113,7 +3125,7 @@
         <v>85</v>
       </c>
       <c r="AJ13" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AK13" s="10" t="s">
         <v>87</v>
@@ -3122,7 +3134,7 @@
         <v>22</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.2">
@@ -4657,34 +4669,34 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B2" s="31"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B3" s="31"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>166</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>167</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>3</v>
@@ -4856,94 +4868,115 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0F4C5A-BE41-6140-9B9B-80B8DB7D1AD7}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22" style="30" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="30" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="30" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" style="30" customWidth="1"/>
-    <col min="7" max="7" width="19" style="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.83203125" style="30" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" style="30" customWidth="1"/>
-    <col min="14" max="14" width="21.5" style="30" customWidth="1"/>
-    <col min="15" max="15" width="23" style="30" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="30"/>
+    <col min="2" max="3" width="22" style="30" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="32.6640625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="30" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" style="30" customWidth="1"/>
+    <col min="8" max="8" width="19" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="30" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5" style="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="30" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" style="30" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.83203125" style="30" customWidth="1"/>
+    <col min="15" max="20" width="21.5" style="30" customWidth="1"/>
+    <col min="21" max="21" width="23" style="30" customWidth="1"/>
+    <col min="22" max="16384" width="8.83203125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="24" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="29"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
-        <v>148</v>
-      </c>
       <c r="B2" s="31"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C2" s="31"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C3" s="31"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="F4" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="O4" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="L4" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="M4" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="N4" s="33" t="s">
+      <c r="P4" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="Q4" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="R4" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="S4" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="U4" s="33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="15"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
@@ -4954,314 +4987,420 @@
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
-      <c r="N5" s="17"/>
+      <c r="N5" s="15"/>
       <c r="O5" s="17"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
-      <c r="C6" s="15"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
-      <c r="N6" s="17"/>
+      <c r="N6" s="15"/>
       <c r="O6" s="17"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
-      <c r="C7" s="15"/>
+      <c r="C7" s="17"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-      <c r="N7" s="17"/>
+      <c r="N7" s="15"/>
       <c r="O7" s="17"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
-      <c r="C8" s="15"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-      <c r="N8" s="17"/>
+      <c r="N8" s="15"/>
       <c r="O8" s="17"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="15"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-      <c r="N9" s="17"/>
+      <c r="N9" s="15"/>
       <c r="O9" s="17"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
-      <c r="C10" s="15"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-      <c r="N10" s="17"/>
+      <c r="N10" s="15"/>
       <c r="O10" s="17"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
-      <c r="C11" s="15"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
-      <c r="N11" s="17"/>
+      <c r="N11" s="15"/>
       <c r="O11" s="17"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
-      <c r="C12" s="15"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
-      <c r="N12" s="17"/>
+      <c r="N12" s="15"/>
       <c r="O12" s="17"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="15"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="15"/>
       <c r="O13" s="17"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="17"/>
+      <c r="N14" s="15"/>
       <c r="O14" s="17"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
-      <c r="N15" s="17"/>
+      <c r="N15" s="15"/>
       <c r="O15" s="17"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
-      <c r="C16" s="15"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="27"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
-      <c r="N16" s="17"/>
+      <c r="N16" s="15"/>
       <c r="O16" s="17"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="27"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
-      <c r="N17" s="17"/>
+      <c r="N17" s="15"/>
       <c r="O17" s="17"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
-      <c r="C18" s="15"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="27"/>
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
-      <c r="N18" s="17"/>
+      <c r="N18" s="15"/>
       <c r="O18" s="17"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
-      <c r="C19" s="15"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
-      <c r="N19" s="17"/>
+      <c r="N19" s="15"/>
       <c r="O19" s="17"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
-      <c r="C20" s="15"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
-      <c r="N20" s="17"/>
+      <c r="N20" s="15"/>
       <c r="O20" s="17"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
-      <c r="C21" s="15"/>
+      <c r="C21" s="17"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
-      <c r="N21" s="17"/>
+      <c r="N21" s="15"/>
       <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E21">
+  <conditionalFormatting sqref="F5:F21">
     <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
-      <formula>C5="sql"</formula>
+      <formula>D5="sql"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F21">
+  <conditionalFormatting sqref="G5:G21">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>C5="library"</formula>
+      <formula>D5="library"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
-    <dataValidation allowBlank="1" sqref="C22:G42" xr:uid="{E994B14B-32F5-D346-A2D5-4948CC9EA8C3}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Data Quality Type" prompt="Data quality rules support different levels/stages of data quality attributes:_x000a__x000a_Text: A human-readable text that describes the quality of the data._x000a_Library rules: A maintained library of commonly-used predefined quality attributes such as rowCount, unique" sqref="C4" xr:uid="{F5034942-1DBE-6649-8226-7716B942E17B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Scheduler" prompt="Name of the scheduler that runs the quality check, such as cron, Airflow, or Github Action." sqref="L5:M21" xr:uid="{32CE7D0C-23F9-9242-8EB2-22364F11133E}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Severity" prompt="The severity of the data quality rule, such as error or warning." sqref="K5:K21" xr:uid="{0F4D661D-23D9-2540-B241-435A8E49610F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Implementation" prompt="The data quality check in the engine's specific format." sqref="J5:J21" xr:uid="{00416CE8-FD1E-374C-B0CF-0FDCB1952802}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Engine" prompt="Required for custom DQ rule: name of the third-party engine being used. Any value is authorized here but common values are soda, greatExpectations, montecarlo, etc." sqref="I5:I21" xr:uid="{0459F568-8532-4048-9CA7-5708CD6DF179}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Threshold Value" prompt="The acutal value for the treshold operator._x000a_For mustBeBetween adn mustNotBeBetween, use [lowerBoundry, upperBoundy] syntax, e.g. [0, 100]." sqref="H5:H21" xr:uid="{E792E24E-6B57-A948-A026-4637119AD944}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Operator" prompt="The comparation operator specifies the condition to validate the rule._x000a_Use it together with the threshold value, e.g. mustBe 0, or mustBeBetween [0,100]_x000a_This is applicable for quality type sql and some library rules." sqref="G5:G21" xr:uid="{15B1EE74-8A6D-3F49-A7EC-55C27203D116}">
+  <dataValidations count="17">
+    <dataValidation allowBlank="1" sqref="D22:H42" xr:uid="{E994B14B-32F5-D346-A2D5-4948CC9EA8C3}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Data Quality Type" prompt="Data quality rules support different levels/stages of data quality attributes:_x000a__x000a_Text: A human-readable text that describes the quality of the data._x000a_Library rules: A maintained library of commonly-used predefined quality attributes such as rowCount, unique" sqref="D4" xr:uid="{F5034942-1DBE-6649-8226-7716B942E17B}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Scheduler" prompt="Name of the scheduler that runs the quality check, such as cron, Airflow, or Github Action." sqref="M5:N21" xr:uid="{32CE7D0C-23F9-9242-8EB2-22364F11133E}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Severity" prompt="The severity of the data quality rule, such as error or warning." sqref="L5:L21" xr:uid="{0F4D661D-23D9-2540-B241-435A8E49610F}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Implementation" prompt="The data quality check in the engine's specific format." sqref="K5:K21" xr:uid="{00416CE8-FD1E-374C-B0CF-0FDCB1952802}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Engine" prompt="Required for custom DQ rule: name of the third-party engine being used. Any value is authorized here but common values are soda, greatExpectations, montecarlo, etc." sqref="J5:J21" xr:uid="{0459F568-8532-4048-9CA7-5708CD6DF179}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Threshold Value" prompt="The acutal value for the treshold operator._x000a_For mustBeBetween adn mustNotBeBetween, use [lowerBoundry, upperBoundy] syntax, e.g. [0, 100]." sqref="I5:I21" xr:uid="{E792E24E-6B57-A948-A026-4637119AD944}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Operator" prompt="The comparation operator specifies the condition to validate the rule._x000a_Use it together with the threshold value, e.g. mustBe 0, or mustBeBetween [0,100]_x000a_This is applicable for quality type sql and some library rules." sqref="H5:H21" xr:uid="{15B1EE74-8A6D-3F49-A7EC-55C27203D116}">
       <formula1>"mustBe, mustNotBe, mustBeGreaterThan, mustBeGreaterOrEqualTo, mustBeLessThan, mustBeLessOrEqualTo, mustBeBetween, mustNotBeBetween"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Query" prompt="A single SQL query that returns either a numeric or boolean value for comparison. The query must be written in the SQL dialect specific to the provided server. " sqref="F5:F21" xr:uid="{21D55077-EE2C-364C-A32A-00F4CC049BEA}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Metric" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="E5:E21" xr:uid="{FA04105D-EE78-664F-8C72-4098B271EC60}">
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality Query" prompt="A single SQL query that returns either a numeric or boolean value for comparison. The query must be written in the SQL dialect specific to the provided server. " sqref="G5:G21" xr:uid="{21D55077-EE2C-364C-A32A-00F4CC049BEA}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Quality Metric" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="F5:F21" xr:uid="{FA04105D-EE78-664F-8C72-4098B271EC60}">
       <formula1>"nullValues,missingValues,invalidValues,duplicateValues,rowCount"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C5:C21" xr:uid="{664F88A2-7556-9B4E-A851-8889D6576B99}">
+    <dataValidation type="list" allowBlank="1" sqref="D5:D21" xr:uid="{664F88A2-7556-9B4E-A851-8889D6576B99}">
       <formula1>"text,library,sql,custom"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="D5:D21" xr:uid="{C84C6FF8-FC8D-B848-AC69-3DB82C6CB871}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Quality" prompt="The expected or guaranteed data quality from a business perspective._x000a__x000a_Maps to quality.description" sqref="E5:E21" xr:uid="{C84C6FF8-FC8D-B848-AC69-3DB82C6CB871}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Schema" prompt="The schema name must match the name of the schema (table, ...) in the previous sheets." sqref="A4" xr:uid="{67CAE90D-676C-A44B-B965-361A399ACA9A}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_" sqref="B4" xr:uid="{F3E67713-E117-6E46-AEFE-6861F5933838}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)" sqref="E4" xr:uid="{4E8AA24F-1E70-FF4C-81CC-D9A25B05246C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Rule" prompt="The predefined data quality rule from the library._x000a_Only appliable if &quot;Quality Type&quot; is set to &quot;library&quot; or empty (which is library by default, if a rule is defined)" sqref="F4" xr:uid="{4E8AA24F-1E70-FF4C-81CC-D9A25B05246C}"/>
+    <dataValidation allowBlank="1" promptTitle="Property" prompt="Optional: Leave empty, if this is a schema-level quality check._x000a_The property must match the property name in the schema._x000a_" sqref="C4" xr:uid="{6AFBB4EF-CE11-8042-AA1B-F7BDF348C368}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P5:P100" xr:uid="{08A9C1F9-48E6-1B4D-AA00-29BFA1FC43C8}">
+      <formula1>"accuracy,completeness,conformity,consistency,coverage,timeliness,uniqueness"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5501,7 +5640,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="5"/>
     </row>
@@ -5732,187 +5871,232 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B433535-9968-AF4C-822D-F1478F01E2E0}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="59.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.1640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="2"/>
+    <col min="1" max="1" width="20.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="59.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="34.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B5:E61 F5:F21" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
+  <dataValidations count="2">
+    <dataValidation allowBlank="1" sqref="D5:G61 H5:H21" xr:uid="{87F0D0D6-8894-A64F-B36D-300F6FA120B5}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A5:A100" xr:uid="{7B083D8C-1D55-F248-A4D8-E7280287A5D3}">
+      <formula1>"Contract,Server"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5937,12 +6121,12 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -5950,7 +6134,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="26"/>
     </row>
@@ -5962,25 +6146,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>105</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>22</v>

--- a/odcs-template-v3.1.xlsx
+++ b/odcs-template-v3.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FE2229-D9E8-0C4D-B44D-DD7BC1E7A83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB73894-B6EC-294D-8F06-D8D512A30D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <definedName name="price.priceUnit">Pricing!$B$6</definedName>
     <definedName name="quality">Quality!$A$4:$BF$300</definedName>
     <definedName name="relationships">Relationships!$A$4:$AZ$300</definedName>
-    <definedName name="roles" localSheetId="7">Roles!$C$4:$H$1000</definedName>
+    <definedName name="roles" localSheetId="7">Roles!$A$4:$AZ$1000</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$8</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema &lt;table_name&gt;'!$B$10</definedName>
     <definedName name="schema.description" localSheetId="2">'Schema &lt;table_name&gt;'!$B$7</definedName>
@@ -908,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1011,7 +1011,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -5891,7 +5890,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="4" t="s">
         <v>178</v>
       </c>
     </row>

--- a/odcs-template-v3.1.xlsx
+++ b/odcs-template-v3.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakob/entropyData/open-data-contract-standard-excel-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB73894-B6EC-294D-8F06-D8D512A30D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBA4A82-F204-A54F-8C91-1807E7B70886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,18 +28,19 @@
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
+    <definedName name="contractCreatedTs">Fundamentals!$C$11</definedName>
     <definedName name="CustomProperties">'Custom Properties'!$A$5:$D$21</definedName>
     <definedName name="datacontract_id">Fundamentals!$C$7</definedName>
-    <definedName name="dataProduct">Fundamentals!$C$15</definedName>
-    <definedName name="description.limitations">Fundamentals!$C$20</definedName>
-    <definedName name="description.purpose">Fundamentals!$C$19</definedName>
-    <definedName name="description.usage">Fundamentals!$C$21</definedName>
-    <definedName name="domain">Fundamentals!$C$14</definedName>
+    <definedName name="dataProduct">Fundamentals!$C$16</definedName>
+    <definedName name="description.limitations">Fundamentals!$C$21</definedName>
+    <definedName name="description.purpose">Fundamentals!$C$20</definedName>
+    <definedName name="description.usage">Fundamentals!$C$22</definedName>
+    <definedName name="domain">Fundamentals!$C$15</definedName>
     <definedName name="id">Fundamentals!$C$7</definedName>
     <definedName name="instructions.importUrl">Instructions!$B$24</definedName>
     <definedName name="kind">Fundamentals!$C$4</definedName>
     <definedName name="name">Fundamentals!$C$8</definedName>
-    <definedName name="owner">Fundamentals!$C$12</definedName>
+    <definedName name="owner">Fundamentals!$C$13</definedName>
     <definedName name="price.id">Pricing!$B$7</definedName>
     <definedName name="price.priceAmount">Pricing!$B$4</definedName>
     <definedName name="price.priceCurrency">Pricing!$B$5</definedName>
@@ -54,7 +55,7 @@
     <definedName name="schema.name" localSheetId="2">'Schema &lt;table_name&gt;'!$B$5</definedName>
     <definedName name="schema.physicalName" localSheetId="2">'Schema &lt;table_name&gt;'!$B$9</definedName>
     <definedName name="schema.physicalType" localSheetId="2">'Schema &lt;table_name&gt;'!$B$6</definedName>
-    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$13:$AM$981</definedName>
+    <definedName name="schema.properties" localSheetId="2">'Schema &lt;table_name&gt;'!$A$13:$AO$981</definedName>
     <definedName name="schema.tags" localSheetId="2">'Schema &lt;table_name&gt;'!$B$11</definedName>
     <definedName name="servers.azure.delimiter">Servers!$C$15</definedName>
     <definedName name="servers.azure.format">Servers!$C$14</definedName>
@@ -119,13 +120,13 @@
     <definedName name="slaProperties" localSheetId="8">SLA!$A$6:$J$1002</definedName>
     <definedName name="status">Fundamentals!$C$10</definedName>
     <definedName name="support">Support!$A$4:$G$1000</definedName>
-    <definedName name="tags">Fundamentals!$C$23</definedName>
-    <definedName name="team">Team!$A$10:$H$1006</definedName>
+    <definedName name="tags">Fundamentals!$C$24</definedName>
+    <definedName name="team">Team!$A$10:$I$1006</definedName>
     <definedName name="team.description">Team!$B$5</definedName>
     <definedName name="team.id">Team!$B$7</definedName>
     <definedName name="team.name">Team!$B$4</definedName>
     <definedName name="team.tags">Team!$B$6</definedName>
-    <definedName name="tenant">Fundamentals!$C$16</definedName>
+    <definedName name="tenant">Fundamentals!$C$17</definedName>
     <definedName name="version">Fundamentals!$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -146,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -689,6 +690,15 @@
   <si>
     <t xml:space="preserve">This section lists the roles that a consumer may need to access the dataset depending on the type of access they require.
 </t>
+  </si>
+  <si>
+    <t>Timezone</t>
+  </si>
+  <si>
+    <t>Default Timezone</t>
+  </si>
+  <si>
+    <t>Contract Created</t>
   </si>
 </sst>
 </file>
@@ -2705,7 +2715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ABE851-FB8B-2145-B7F8-5CF6722D55A6}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="2" customWidth="1"/>
@@ -2783,32 +2793,31 @@
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>181</v>
+      </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="5"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="5"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="A14" s="7"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="5"/>
-      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="5"/>
@@ -2816,66 +2825,74 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="7"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="5"/>
+      <c r="B19" s="7"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="5"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="G11:L13 G23:L24 G17:L22" xr:uid="{7EB39568-B879-514E-B51D-6C44C6D6A95F}">
+    <dataValidation type="list" allowBlank="1" sqref="G12:L14 G18:L25" xr:uid="{7EB39568-B879-514E-B51D-6C44C6D6A95F}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D22 D17:D18 D11:D13 D24" xr:uid="{1D2456BD-0546-F940-A9EF-51615EED43D0}">
+    <dataValidation type="list" allowBlank="1" sqref="D23 D18:D19 D12:D14 D25" xr:uid="{1D2456BD-0546-F940-A9EF-51615EED43D0}">
       <formula1>"string,number,integer,boolean,array,object"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Owner" prompt="The ID of the team owning the Data Contract._x000a_Required for Data Mesh Manager." sqref="C12" xr:uid="{35986E89-F1AF-D84C-96AD-8E5AC4A64A86}"/>
-    <dataValidation allowBlank="1" sqref="C11:C13 C17:C18 C22:C65" xr:uid="{D875F021-2666-244F-B1D7-40151775E3CC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Owner" prompt="The ID of the team owning the Data Contract._x000a_Required for Data Mesh Manager." sqref="C13" xr:uid="{35986E89-F1AF-D84C-96AD-8E5AC4A64A86}"/>
+    <dataValidation allowBlank="1" sqref="C12:C14 C18:C19 C23:C66" xr:uid="{D875F021-2666-244F-B1D7-40151775E3CC}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2884,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AO49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
@@ -2904,27 +2921,27 @@
     <col min="16" max="20" width="19" style="2" customWidth="1"/>
     <col min="21" max="21" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="38" width="15.5" style="2" customWidth="1"/>
-    <col min="39" max="39" width="26.1640625" style="2" customWidth="1"/>
-    <col min="40" max="16384" width="8.83203125" style="2"/>
+    <col min="23" max="40" width="15.5" style="2" customWidth="1"/>
+    <col min="41" max="41" width="26.1640625" style="2" customWidth="1"/>
+    <col min="42" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
@@ -2935,7 +2952,7 @@
       <c r="D5" s="36"/>
       <c r="E5" s="36"/>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
@@ -2946,7 +2963,7 @@
       <c r="D6" s="36"/>
       <c r="E6" s="36"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2955,7 +2972,7 @@
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
@@ -2964,7 +2981,7 @@
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
@@ -2973,7 +2990,7 @@
       <c r="D9" s="38"/>
       <c r="E9" s="39"/>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>52</v>
       </c>
@@ -2982,7 +2999,7 @@
       <c r="D10" s="38"/>
       <c r="E10" s="39"/>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
@@ -2991,7 +3008,7 @@
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
@@ -3015,9 +3032,11 @@
       <c r="AH12" s="20"/>
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
-      <c r="AK12" s="21"/>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AK12" s="20"/>
+      <c r="AL12" s="20"/>
+      <c r="AM12" s="21"/>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>0</v>
       </c>
@@ -3130,13 +3149,19 @@
         <v>87</v>
       </c>
       <c r="AL13" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="AM13" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AN13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="AM13" s="10" t="s">
+      <c r="AO13" s="10" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
@@ -3175,9 +3200,11 @@
       <c r="AJ14" s="15"/>
       <c r="AK14" s="15"/>
       <c r="AL14" s="15"/>
-      <c r="AM14" s="28"/>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM14" s="15"/>
+      <c r="AN14" s="15"/>
+      <c r="AO14" s="28"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -3216,9 +3243,11 @@
       <c r="AJ15" s="15"/>
       <c r="AK15" s="15"/>
       <c r="AL15" s="15"/>
-      <c r="AM15" s="28"/>
-    </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM15" s="15"/>
+      <c r="AN15" s="15"/>
+      <c r="AO15" s="28"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -3257,9 +3286,11 @@
       <c r="AJ16" s="15"/>
       <c r="AK16" s="15"/>
       <c r="AL16" s="15"/>
-      <c r="AM16" s="28"/>
-    </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM16" s="15"/>
+      <c r="AN16" s="15"/>
+      <c r="AO16" s="28"/>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -3298,9 +3329,11 @@
       <c r="AJ17" s="15"/>
       <c r="AK17" s="15"/>
       <c r="AL17" s="15"/>
-      <c r="AM17" s="28"/>
-    </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM17" s="15"/>
+      <c r="AN17" s="15"/>
+      <c r="AO17" s="28"/>
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -3339,9 +3372,11 @@
       <c r="AJ18" s="15"/>
       <c r="AK18" s="15"/>
       <c r="AL18" s="15"/>
-      <c r="AM18" s="28"/>
-    </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM18" s="15"/>
+      <c r="AN18" s="15"/>
+      <c r="AO18" s="28"/>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -3380,9 +3415,11 @@
       <c r="AJ19" s="15"/>
       <c r="AK19" s="15"/>
       <c r="AL19" s="15"/>
-      <c r="AM19" s="28"/>
-    </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM19" s="15"/>
+      <c r="AN19" s="15"/>
+      <c r="AO19" s="28"/>
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -3421,9 +3458,11 @@
       <c r="AJ20" s="15"/>
       <c r="AK20" s="15"/>
       <c r="AL20" s="15"/>
-      <c r="AM20" s="28"/>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM20" s="15"/>
+      <c r="AN20" s="15"/>
+      <c r="AO20" s="28"/>
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A21" s="18"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -3462,9 +3501,11 @@
       <c r="AJ21" s="15"/>
       <c r="AK21" s="15"/>
       <c r="AL21" s="15"/>
-      <c r="AM21" s="28"/>
-    </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM21" s="15"/>
+      <c r="AN21" s="15"/>
+      <c r="AO21" s="28"/>
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A22" s="18"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -3503,9 +3544,11 @@
       <c r="AJ22" s="15"/>
       <c r="AK22" s="15"/>
       <c r="AL22" s="15"/>
-      <c r="AM22" s="28"/>
-    </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM22" s="15"/>
+      <c r="AN22" s="15"/>
+      <c r="AO22" s="28"/>
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A23" s="18"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -3544,9 +3587,11 @@
       <c r="AJ23" s="15"/>
       <c r="AK23" s="15"/>
       <c r="AL23" s="15"/>
-      <c r="AM23" s="28"/>
-    </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM23" s="15"/>
+      <c r="AN23" s="15"/>
+      <c r="AO23" s="28"/>
+    </row>
+    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A24" s="17"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -3585,9 +3630,11 @@
       <c r="AJ24" s="15"/>
       <c r="AK24" s="15"/>
       <c r="AL24" s="15"/>
-      <c r="AM24" s="28"/>
-    </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM24" s="15"/>
+      <c r="AN24" s="15"/>
+      <c r="AO24" s="28"/>
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A25" s="17"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -3626,9 +3673,11 @@
       <c r="AJ25" s="15"/>
       <c r="AK25" s="15"/>
       <c r="AL25" s="15"/>
-      <c r="AM25" s="28"/>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM25" s="15"/>
+      <c r="AN25" s="15"/>
+      <c r="AO25" s="28"/>
+    </row>
+    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A26" s="17"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -3667,9 +3716,11 @@
       <c r="AJ26" s="15"/>
       <c r="AK26" s="15"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="28"/>
-    </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM26" s="15"/>
+      <c r="AN26" s="15"/>
+      <c r="AO26" s="28"/>
+    </row>
+    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A27" s="17"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -3708,9 +3759,11 @@
       <c r="AJ27" s="15"/>
       <c r="AK27" s="15"/>
       <c r="AL27" s="15"/>
-      <c r="AM27" s="28"/>
-    </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="28"/>
+    </row>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A28" s="17"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -3749,9 +3802,11 @@
       <c r="AJ28" s="15"/>
       <c r="AK28" s="15"/>
       <c r="AL28" s="15"/>
-      <c r="AM28" s="28"/>
-    </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM28" s="15"/>
+      <c r="AN28" s="15"/>
+      <c r="AO28" s="28"/>
+    </row>
+    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A29" s="17"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -3790,9 +3845,11 @@
       <c r="AJ29" s="15"/>
       <c r="AK29" s="15"/>
       <c r="AL29" s="15"/>
-      <c r="AM29" s="28"/>
-    </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM29" s="15"/>
+      <c r="AN29" s="15"/>
+      <c r="AO29" s="28"/>
+    </row>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A30" s="17"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -3831,9 +3888,11 @@
       <c r="AJ30" s="15"/>
       <c r="AK30" s="15"/>
       <c r="AL30" s="15"/>
-      <c r="AM30" s="28"/>
-    </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM30" s="15"/>
+      <c r="AN30" s="15"/>
+      <c r="AO30" s="28"/>
+    </row>
+    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A31" s="17"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -3872,9 +3931,11 @@
       <c r="AJ31" s="15"/>
       <c r="AK31" s="15"/>
       <c r="AL31" s="15"/>
-      <c r="AM31" s="28"/>
-    </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM31" s="15"/>
+      <c r="AN31" s="15"/>
+      <c r="AO31" s="28"/>
+    </row>
+    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A32" s="17"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -3913,9 +3974,11 @@
       <c r="AJ32" s="15"/>
       <c r="AK32" s="15"/>
       <c r="AL32" s="15"/>
-      <c r="AM32" s="28"/>
-    </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM32" s="15"/>
+      <c r="AN32" s="15"/>
+      <c r="AO32" s="28"/>
+    </row>
+    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A33" s="17"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -3954,9 +4017,11 @@
       <c r="AJ33" s="15"/>
       <c r="AK33" s="15"/>
       <c r="AL33" s="15"/>
-      <c r="AM33" s="28"/>
-    </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM33" s="15"/>
+      <c r="AN33" s="15"/>
+      <c r="AO33" s="28"/>
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -3995,9 +4060,11 @@
       <c r="AJ34" s="15"/>
       <c r="AK34" s="15"/>
       <c r="AL34" s="15"/>
-      <c r="AM34" s="28"/>
-    </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM34" s="15"/>
+      <c r="AN34" s="15"/>
+      <c r="AO34" s="28"/>
+    </row>
+    <row r="35" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -4036,9 +4103,11 @@
       <c r="AJ35" s="15"/>
       <c r="AK35" s="15"/>
       <c r="AL35" s="15"/>
-      <c r="AM35" s="28"/>
-    </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM35" s="15"/>
+      <c r="AN35" s="15"/>
+      <c r="AO35" s="28"/>
+    </row>
+    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -4077,9 +4146,11 @@
       <c r="AJ36" s="15"/>
       <c r="AK36" s="15"/>
       <c r="AL36" s="15"/>
-      <c r="AM36" s="28"/>
-    </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM36" s="15"/>
+      <c r="AN36" s="15"/>
+      <c r="AO36" s="28"/>
+    </row>
+    <row r="37" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -4118,9 +4189,11 @@
       <c r="AJ37" s="15"/>
       <c r="AK37" s="15"/>
       <c r="AL37" s="15"/>
-      <c r="AM37" s="28"/>
-    </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM37" s="15"/>
+      <c r="AN37" s="15"/>
+      <c r="AO37" s="28"/>
+    </row>
+    <row r="38" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -4159,9 +4232,11 @@
       <c r="AJ38" s="15"/>
       <c r="AK38" s="15"/>
       <c r="AL38" s="15"/>
-      <c r="AM38" s="28"/>
-    </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM38" s="15"/>
+      <c r="AN38" s="15"/>
+      <c r="AO38" s="28"/>
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A39" s="17"/>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -4200,9 +4275,11 @@
       <c r="AJ39" s="15"/>
       <c r="AK39" s="15"/>
       <c r="AL39" s="15"/>
-      <c r="AM39" s="28"/>
-    </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM39" s="15"/>
+      <c r="AN39" s="15"/>
+      <c r="AO39" s="28"/>
+    </row>
+    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A40" s="17"/>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -4241,9 +4318,11 @@
       <c r="AJ40" s="15"/>
       <c r="AK40" s="15"/>
       <c r="AL40" s="15"/>
-      <c r="AM40" s="28"/>
-    </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM40" s="15"/>
+      <c r="AN40" s="15"/>
+      <c r="AO40" s="28"/>
+    </row>
+    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A41" s="17"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -4282,9 +4361,11 @@
       <c r="AJ41" s="15"/>
       <c r="AK41" s="15"/>
       <c r="AL41" s="15"/>
-      <c r="AM41" s="28"/>
-    </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM41" s="15"/>
+      <c r="AN41" s="15"/>
+      <c r="AO41" s="28"/>
+    </row>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A42" s="17"/>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -4323,9 +4404,11 @@
       <c r="AJ42" s="15"/>
       <c r="AK42" s="15"/>
       <c r="AL42" s="15"/>
-      <c r="AM42" s="28"/>
-    </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM42" s="15"/>
+      <c r="AN42" s="15"/>
+      <c r="AO42" s="28"/>
+    </row>
+    <row r="43" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A43" s="17"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -4364,9 +4447,11 @@
       <c r="AJ43" s="15"/>
       <c r="AK43" s="15"/>
       <c r="AL43" s="15"/>
-      <c r="AM43" s="28"/>
-    </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM43" s="15"/>
+      <c r="AN43" s="15"/>
+      <c r="AO43" s="28"/>
+    </row>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A44" s="17"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -4405,9 +4490,11 @@
       <c r="AJ44" s="15"/>
       <c r="AK44" s="15"/>
       <c r="AL44" s="15"/>
-      <c r="AM44" s="28"/>
-    </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM44" s="15"/>
+      <c r="AN44" s="15"/>
+      <c r="AO44" s="28"/>
+    </row>
+    <row r="45" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A45" s="17"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -4446,9 +4533,11 @@
       <c r="AJ45" s="15"/>
       <c r="AK45" s="15"/>
       <c r="AL45" s="15"/>
-      <c r="AM45" s="28"/>
-    </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM45" s="15"/>
+      <c r="AN45" s="15"/>
+      <c r="AO45" s="28"/>
+    </row>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A46" s="17"/>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -4487,9 +4576,11 @@
       <c r="AJ46" s="15"/>
       <c r="AK46" s="15"/>
       <c r="AL46" s="15"/>
-      <c r="AM46" s="28"/>
-    </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM46" s="15"/>
+      <c r="AN46" s="15"/>
+      <c r="AO46" s="28"/>
+    </row>
+    <row r="47" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A47" s="17"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -4528,9 +4619,11 @@
       <c r="AJ47" s="15"/>
       <c r="AK47" s="15"/>
       <c r="AL47" s="15"/>
-      <c r="AM47" s="28"/>
-    </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM47" s="15"/>
+      <c r="AN47" s="15"/>
+      <c r="AO47" s="28"/>
+    </row>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A48" s="17"/>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -4569,9 +4662,11 @@
       <c r="AJ48" s="15"/>
       <c r="AK48" s="15"/>
       <c r="AL48" s="15"/>
-      <c r="AM48" s="28"/>
-    </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AM48" s="15"/>
+      <c r="AN48" s="15"/>
+      <c r="AO48" s="28"/>
+    </row>
+    <row r="49" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A49" s="17"/>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -4610,7 +4705,9 @@
       <c r="AJ49" s="15"/>
       <c r="AK49" s="15"/>
       <c r="AL49" s="15"/>
-      <c r="AM49" s="28"/>
+      <c r="AM49" s="15"/>
+      <c r="AN49" s="15"/>
+      <c r="AO49" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4623,14 +4720,14 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Unique" prompt="A value must be unique within the dataset" sqref="H14:H49" xr:uid="{274C493E-CBE0-2742-BFD6-A161E5736B5A}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C49" xr:uid="{792BC06D-75E6-1A4B-8EE7-26D8A0C4CF46}">
       <formula1>"string,number,integer,boolean,array,object,timestamp,date,time"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="B14:B49 J14:J49 M14:U49 W14:AM49" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
+    <dataValidation allowBlank="1" sqref="B14:B49 J14:J49 M14:U49 W14:AK49 AM14:AO49" xr:uid="{DDC4FF9F-5023-E04B-9FAD-8E0C431863DF}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Required" prompt="Is this a required field (true) or can it be optional (false)" sqref="G14:G49" xr:uid="{653181B6-028C-9348-B6A1-78F7EF7B9A52}">
       <formula1>"true,false"</formula1>
     </dataValidation>
@@ -4646,7 +4743,10 @@
     <dataValidation type="list" allowBlank="1" sqref="V14:V49" xr:uid="{17C32F0F-20AB-664B-ABCA-B45524F93539}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AM13" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Comments" prompt="Use this for internal comments, open questions, discussion points. _x000a_This will not become part of the ODCS YAML." sqref="AO13" xr:uid="{D669647A-617C-7549-9EA2-AC37BFEA6E41}"/>
+    <dataValidation type="list" allowBlank="1" sqref="AL14:AL100" xr:uid="{C918BD77-1398-7446-8AAC-BAE751FE6F3F}">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5614,57 +5714,57 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD55E6DF-E5C5-C142-BA93-791862A30BE7}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" style="2" customWidth="1"/>
     <col min="2" max="3" width="59.6640625" style="2" customWidth="1"/>
-    <col min="4" max="7" width="23.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.5" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="2"/>
+    <col min="4" max="8" width="23.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>169</v>
       </c>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>62</v>
       </c>
@@ -5678,19 +5778,22 @@
         <v>63</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="I10" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -5699,8 +5802,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -5709,8 +5813,9 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -5719,8 +5824,9 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -5729,8 +5835,9 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -5739,8 +5846,9 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -5749,8 +5857,9 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -5759,8 +5868,9 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -5769,8 +5879,9 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -5779,8 +5890,9 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -5789,8 +5901,9 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -5799,8 +5912,9 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -5809,8 +5923,9 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -5819,8 +5934,9 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -5829,8 +5945,9 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -5839,8 +5956,9 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -5849,8 +5967,9 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -5859,10 +5978,11 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="B11:G67 H11:H27" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
+    <dataValidation allowBlank="1" sqref="B11:H67 I11:I27" xr:uid="{8BD676B5-0F0C-9D41-BB36-24C33963E434}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
